--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6196"/>
+  <dimension ref="A1:B6203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74776,7 +74776,91 @@
       </c>
       <c r="B6196" t="inlineStr">
         <is>
-          <t>87917.8000000000</t>
+          <t>87133.5103991818</t>
+        </is>
+      </c>
+    </row>
+    <row r="6197">
+      <c r="A6197" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B6197" t="inlineStr">
+        <is>
+          <t>88428.4922735243</t>
+        </is>
+      </c>
+    </row>
+    <row r="6198">
+      <c r="A6198" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B6198" t="inlineStr">
+        <is>
+          <t>87516.9780376972</t>
+        </is>
+      </c>
+    </row>
+    <row r="6199">
+      <c r="A6199" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B6199" t="inlineStr">
+        <is>
+          <t>88684.2178474576</t>
+        </is>
+      </c>
+    </row>
+    <row r="6200">
+      <c r="A6200" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B6200" t="inlineStr">
+        <is>
+          <t>89940.1801671537</t>
+        </is>
+      </c>
+    </row>
+    <row r="6201">
+      <c r="A6201" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B6201" t="inlineStr">
+        <is>
+          <t>90598.1301832262</t>
+        </is>
+      </c>
+    </row>
+    <row r="6202">
+      <c r="A6202" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B6202" t="inlineStr">
+        <is>
+          <t>90649.0100000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6203">
+      <c r="A6203" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B6203" t="inlineStr">
+        <is>
+          <t>91294.9900000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6203"/>
+  <dimension ref="A1:B6206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74848,7 +74848,7 @@
       </c>
       <c r="B6202" t="inlineStr">
         <is>
-          <t>90649.0100000000</t>
+          <t>91359.7636823495</t>
         </is>
       </c>
     </row>
@@ -74860,7 +74860,43 @@
       </c>
       <c r="B6203" t="inlineStr">
         <is>
-          <t>91294.9900000000</t>
+          <t>93948.5821794272</t>
+        </is>
+      </c>
+    </row>
+    <row r="6204">
+      <c r="A6204" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B6204" t="inlineStr">
+        <is>
+          <t>93574.2871122151</t>
+        </is>
+      </c>
+    </row>
+    <row r="6205">
+      <c r="A6205" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B6205" t="inlineStr">
+        <is>
+          <t>91208.9562606663</t>
+        </is>
+      </c>
+    </row>
+    <row r="6206">
+      <c r="A6206" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B6206" t="inlineStr">
+        <is>
+          <t>91093.4100000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6206"/>
+  <dimension ref="A1:B6209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74896,7 +74896,43 @@
       </c>
       <c r="B6206" t="inlineStr">
         <is>
-          <t>91093.4100000000</t>
+          <t>91096.9161554647</t>
+        </is>
+      </c>
+    </row>
+    <row r="6207">
+      <c r="A6207" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B6207" t="inlineStr">
+        <is>
+          <t>90539.6032288136</t>
+        </is>
+      </c>
+    </row>
+    <row r="6208">
+      <c r="A6208" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B6208" t="inlineStr">
+        <is>
+          <t>90630.0900000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6209">
+      <c r="A6209" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B6209" t="inlineStr">
+        <is>
+          <t>90444.9800000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6209"/>
+  <dimension ref="A1:B6212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74920,7 +74920,7 @@
       </c>
       <c r="B6208" t="inlineStr">
         <is>
-          <t>90630.0900000000</t>
+          <t>90406.1424114553</t>
         </is>
       </c>
     </row>
@@ -74932,7 +74932,43 @@
       </c>
       <c r="B6209" t="inlineStr">
         <is>
-          <t>90444.9800000000</t>
+          <t>90717.2063153127</t>
+        </is>
+      </c>
+    </row>
+    <row r="6210">
+      <c r="A6210" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B6210" t="inlineStr">
+        <is>
+          <t>91141.1498489188</t>
+        </is>
+      </c>
+    </row>
+    <row r="6211">
+      <c r="A6211" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B6211" t="inlineStr">
+        <is>
+          <t>95304.4982942724</t>
+        </is>
+      </c>
+    </row>
+    <row r="6212">
+      <c r="A6212" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B6212" t="inlineStr">
+        <is>
+          <t>95896.6400000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6212"/>
+  <dimension ref="A1:B6217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74968,7 +74968,67 @@
       </c>
       <c r="B6212" t="inlineStr">
         <is>
-          <t>95896.6400000000</t>
+          <t>97043.9927258913</t>
+        </is>
+      </c>
+    </row>
+    <row r="6213">
+      <c r="A6213" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B6213" t="inlineStr">
+        <is>
+          <t>95546.1397381648</t>
+        </is>
+      </c>
+    </row>
+    <row r="6214">
+      <c r="A6214" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6214" t="inlineStr">
+        <is>
+          <t>95489.1299602572</t>
+        </is>
+      </c>
+    </row>
+    <row r="6215">
+      <c r="A6215" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B6215" t="inlineStr">
+        <is>
+          <t>95106.9804625950</t>
+        </is>
+      </c>
+    </row>
+    <row r="6216">
+      <c r="A6216" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B6216" t="inlineStr">
+        <is>
+          <t>95177.2400000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6217">
+      <c r="A6217" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B6217" t="inlineStr">
+        <is>
+          <t>95465.4900000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6217"/>
+  <dimension ref="A1:B6220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75016,7 +75016,7 @@
       </c>
       <c r="B6216" t="inlineStr">
         <is>
-          <t>95177.2400000000</t>
+          <t>94261.3294313267</t>
         </is>
       </c>
     </row>
@@ -75028,7 +75028,43 @@
       </c>
       <c r="B6217" t="inlineStr">
         <is>
-          <t>95465.4900000000</t>
+          <t>92526.2419643483</t>
+        </is>
+      </c>
+    </row>
+    <row r="6218">
+      <c r="A6218" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B6218" t="inlineStr">
+        <is>
+          <t>88236.5631922852</t>
+        </is>
+      </c>
+    </row>
+    <row r="6219">
+      <c r="A6219" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B6219" t="inlineStr">
+        <is>
+          <t>89599.3618749270</t>
+        </is>
+      </c>
+    </row>
+    <row r="6220">
+      <c r="A6220" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B6220" t="inlineStr">
+        <is>
+          <t>89798.0800000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6220"/>
+  <dimension ref="A1:B6224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75064,7 +75064,55 @@
       </c>
       <c r="B6220" t="inlineStr">
         <is>
-          <t>89798.0800000000</t>
+          <t>89395.7007358270</t>
+        </is>
+      </c>
+    </row>
+    <row r="6221">
+      <c r="A6221" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B6221" t="inlineStr">
+        <is>
+          <t>89439.7718909994</t>
+        </is>
+      </c>
+    </row>
+    <row r="6222">
+      <c r="A6222" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B6222" t="inlineStr">
+        <is>
+          <t>89185.0386990064</t>
+        </is>
+      </c>
+    </row>
+    <row r="6223">
+      <c r="A6223" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B6223" t="inlineStr">
+        <is>
+          <t>86445.6705926359</t>
+        </is>
+      </c>
+    </row>
+    <row r="6224">
+      <c r="A6224" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B6224" t="inlineStr">
+        <is>
+          <t>86270.9900000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6224"/>
+  <dimension ref="A1:B6226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75112,7 +75112,31 @@
       </c>
       <c r="B6224" t="inlineStr">
         <is>
-          <t>86270.9900000000</t>
+          <t>88337.4545511397</t>
+        </is>
+      </c>
+    </row>
+    <row r="6225">
+      <c r="A6225" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B6225" t="inlineStr">
+        <is>
+          <t>89260.3805397429</t>
+        </is>
+      </c>
+    </row>
+    <row r="6226">
+      <c r="A6226" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B6226" t="inlineStr">
+        <is>
+          <t>89224.4900000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6226"/>
+  <dimension ref="A1:B6228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75136,7 +75136,31 @@
       </c>
       <c r="B6226" t="inlineStr">
         <is>
-          <t>89224.4900000000</t>
+          <t>89177.7892507306</t>
+        </is>
+      </c>
+    </row>
+    <row r="6227">
+      <c r="A6227" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B6227" t="inlineStr">
+        <is>
+          <t>84520.3973106371</t>
+        </is>
+      </c>
+    </row>
+    <row r="6228">
+      <c r="A6228" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B6228" t="inlineStr">
+        <is>
+          <t>84500.0000000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6228"/>
+  <dimension ref="A1:B6231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75160,7 +75160,43 @@
       </c>
       <c r="B6228" t="inlineStr">
         <is>
-          <t>84500.0000000000</t>
+          <t>84017.0340292227</t>
+        </is>
+      </c>
+    </row>
+    <row r="6229">
+      <c r="A6229" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B6229" t="inlineStr">
+        <is>
+          <t>78702.3855026300</t>
+        </is>
+      </c>
+    </row>
+    <row r="6230">
+      <c r="A6230" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B6230" t="inlineStr">
+        <is>
+          <t>76911.0523772648</t>
+        </is>
+      </c>
+    </row>
+    <row r="6231">
+      <c r="A6231" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B6231" t="inlineStr">
+        <is>
+          <t>77183.0400000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6231"/>
+  <dimension ref="A1:B6233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75196,7 +75196,31 @@
       </c>
       <c r="B6231" t="inlineStr">
         <is>
-          <t>77183.0400000000</t>
+          <t>78716.6018088837</t>
+        </is>
+      </c>
+    </row>
+    <row r="6232">
+      <c r="A6232" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B6232" t="inlineStr">
+        <is>
+          <t>75684.7660277616</t>
+        </is>
+      </c>
+    </row>
+    <row r="6233">
+      <c r="A6233" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B6233" t="inlineStr">
+        <is>
+          <t>75581.4900000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6233"/>
+  <dimension ref="A1:B6235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75220,7 +75220,31 @@
       </c>
       <c r="B6233" t="inlineStr">
         <is>
-          <t>75581.4900000000</t>
+          <t>73095.1914646406</t>
+        </is>
+      </c>
+    </row>
+    <row r="6234">
+      <c r="A6234" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B6234" t="inlineStr">
+        <is>
+          <t>63494.6884456458</t>
+        </is>
+      </c>
+    </row>
+    <row r="6235">
+      <c r="A6235" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B6235" t="inlineStr">
+        <is>
+          <t>63967.1200000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6235"/>
+  <dimension ref="A1:B6239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75244,7 +75244,55 @@
       </c>
       <c r="B6235" t="inlineStr">
         <is>
-          <t>63967.1200000000</t>
+          <t>70647.6982188778</t>
+        </is>
+      </c>
+    </row>
+    <row r="6236">
+      <c r="A6236" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B6236" t="inlineStr">
+        <is>
+          <t>69166.2594424313</t>
+        </is>
+      </c>
+    </row>
+    <row r="6237">
+      <c r="A6237" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B6237" t="inlineStr">
+        <is>
+          <t>70522.5892393337</t>
+        </is>
+      </c>
+    </row>
+    <row r="6238">
+      <c r="A6238" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B6238" t="inlineStr">
+        <is>
+          <t>70244.1017773232</t>
+        </is>
+      </c>
+    </row>
+    <row r="6239">
+      <c r="A6239" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B6239" t="inlineStr">
+        <is>
+          <t>70375.4500000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6239"/>
+  <dimension ref="A1:B6244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75292,7 +75292,67 @@
       </c>
       <c r="B6239" t="inlineStr">
         <is>
-          <t>70375.4500000000</t>
+          <t>68688.7931133840</t>
+        </is>
+      </c>
+    </row>
+    <row r="6240">
+      <c r="A6240" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B6240" t="inlineStr">
+        <is>
+          <t>66989.7165920514</t>
+        </is>
+      </c>
+    </row>
+    <row r="6241">
+      <c r="A6241" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B6241" t="inlineStr">
+        <is>
+          <t>66221.5443115137</t>
+        </is>
+      </c>
+    </row>
+    <row r="6242">
+      <c r="A6242" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B6242" t="inlineStr">
+        <is>
+          <t>68860.8411633548</t>
+        </is>
+      </c>
+    </row>
+    <row r="6243">
+      <c r="A6243" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B6243" t="inlineStr">
+        <is>
+          <t>68949.5700000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6244">
+      <c r="A6244" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B6244" t="inlineStr">
+        <is>
+          <t>69977.9300000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6244"/>
+  <dimension ref="A1:B6248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75340,7 +75340,7 @@
       </c>
       <c r="B6243" t="inlineStr">
         <is>
-          <t>68949.5700000000</t>
+          <t>69798.0791253653</t>
         </is>
       </c>
     </row>
@@ -75352,7 +75352,55 @@
       </c>
       <c r="B6244" t="inlineStr">
         <is>
-          <t>69977.9300000000</t>
+          <t>68629.9599760374</t>
+        </is>
+      </c>
+    </row>
+    <row r="6245">
+      <c r="A6245" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B6245" t="inlineStr">
+        <is>
+          <t>68747.4380286383</t>
+        </is>
+      </c>
+    </row>
+    <row r="6246">
+      <c r="A6246" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B6246" t="inlineStr">
+        <is>
+          <t>67471.0508465809</t>
+        </is>
+      </c>
+    </row>
+    <row r="6247">
+      <c r="A6247" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B6247" t="inlineStr">
+        <is>
+          <t>66380.7069611339</t>
+        </is>
+      </c>
+    </row>
+    <row r="6248">
+      <c r="A6248" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B6248" t="inlineStr">
+        <is>
+          <t>66374.5600000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6248"/>
+  <dimension ref="A1:B6252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75400,7 +75400,55 @@
       </c>
       <c r="B6248" t="inlineStr">
         <is>
-          <t>66374.5600000000</t>
+          <t>66932.3522118644</t>
+        </is>
+      </c>
+    </row>
+    <row r="6249">
+      <c r="A6249" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B6249" t="inlineStr">
+        <is>
+          <t>67977.3092612507</t>
+        </is>
+      </c>
+    </row>
+    <row r="6250">
+      <c r="A6250" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B6250" t="inlineStr">
+        <is>
+          <t>68020.6677612507</t>
+        </is>
+      </c>
+    </row>
+    <row r="6251">
+      <c r="A6251" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B6251" t="inlineStr">
+        <is>
+          <t>67550.0240768556</t>
+        </is>
+      </c>
+    </row>
+    <row r="6252">
+      <c r="A6252" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B6252" t="inlineStr">
+        <is>
+          <t>67690.6000000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6252"/>
+  <dimension ref="A1:B6254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75448,7 +75448,31 @@
       </c>
       <c r="B6252" t="inlineStr">
         <is>
-          <t>67690.6000000000</t>
+          <t>64689.9123308007</t>
+        </is>
+      </c>
+    </row>
+    <row r="6253">
+      <c r="A6253" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B6253" t="inlineStr">
+        <is>
+          <t>64123.7510780245</t>
+        </is>
+      </c>
+    </row>
+    <row r="6254">
+      <c r="A6254" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B6254" t="inlineStr">
+        <is>
+          <t>64122.6000000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6254"/>
+  <dimension ref="A1:B6256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75472,7 +75472,31 @@
       </c>
       <c r="B6254" t="inlineStr">
         <is>
-          <t>64122.6000000000</t>
+          <t>68038.5221794272</t>
+        </is>
+      </c>
+    </row>
+    <row r="6255">
+      <c r="A6255" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B6255" t="inlineStr">
+        <is>
+          <t>67519.2645292227</t>
+        </is>
+      </c>
+    </row>
+    <row r="6256">
+      <c r="A6256" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B6256" t="inlineStr">
+        <is>
+          <t>67480.6100000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6256"/>
+  <dimension ref="A1:B6260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75496,7 +75496,55 @@
       </c>
       <c r="B6256" t="inlineStr">
         <is>
-          <t>67480.6100000000</t>
+          <t>65864.1358170661</t>
+        </is>
+      </c>
+    </row>
+    <row r="6257">
+      <c r="A6257" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B6257" t="inlineStr">
+        <is>
+          <t>66965.6353091759</t>
+        </is>
+      </c>
+    </row>
+    <row r="6258">
+      <c r="A6258" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B6258" t="inlineStr">
+        <is>
+          <t>65733.5212597896</t>
+        </is>
+      </c>
+    </row>
+    <row r="6259">
+      <c r="A6259" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B6259" t="inlineStr">
+        <is>
+          <t>68922.6242974869</t>
+        </is>
+      </c>
+    </row>
+    <row r="6260">
+      <c r="A6260" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B6260" t="inlineStr">
+        <is>
+          <t>69414.7800000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6260"/>
+  <dimension ref="A1:B6263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75544,7 +75544,43 @@
       </c>
       <c r="B6260" t="inlineStr">
         <is>
-          <t>69414.7800000000</t>
+          <t>68431.1740306838</t>
+        </is>
+      </c>
+    </row>
+    <row r="6261">
+      <c r="A6261" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B6261" t="inlineStr">
+        <is>
+          <t>72667.4630575687</t>
+        </is>
+      </c>
+    </row>
+    <row r="6262">
+      <c r="A6262" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B6262" t="inlineStr">
+        <is>
+          <t>70987.4271765050</t>
+        </is>
+      </c>
+    </row>
+    <row r="6263">
+      <c r="A6263" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B6263" t="inlineStr">
+        <is>
+          <t>71213.6200000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6263"/>
+  <dimension ref="A1:B6268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75580,7 +75580,67 @@
       </c>
       <c r="B6263" t="inlineStr">
         <is>
-          <t>71213.6200000000</t>
+          <t>68226.7053927528</t>
+        </is>
+      </c>
+    </row>
+    <row r="6264">
+      <c r="A6264" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B6264" t="inlineStr">
+        <is>
+          <t>67315.5529135009</t>
+        </is>
+      </c>
+    </row>
+    <row r="6265">
+      <c r="A6265" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B6265" t="inlineStr">
+        <is>
+          <t>66202.6978731736</t>
+        </is>
+      </c>
+    </row>
+    <row r="6266">
+      <c r="A6266" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B6266" t="inlineStr">
+        <is>
+          <t>68528.5384699007</t>
+        </is>
+      </c>
+    </row>
+    <row r="6267">
+      <c r="A6267" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B6267" t="inlineStr">
+        <is>
+          <t>68653.0300000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6268">
+      <c r="A6268" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B6268" t="inlineStr">
+        <is>
+          <t>69756.9300000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6268"/>
+  <dimension ref="A1:B6273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75628,7 +75628,7 @@
       </c>
       <c r="B6267" t="inlineStr">
         <is>
-          <t>68653.0300000000</t>
+          <t>69891.8238576856</t>
         </is>
       </c>
     </row>
@@ -75640,7 +75640,67 @@
       </c>
       <c r="B6268" t="inlineStr">
         <is>
-          <t>69756.9300000000</t>
+          <t>70298.5753530099</t>
+        </is>
+      </c>
+    </row>
+    <row r="6269">
+      <c r="A6269" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B6269" t="inlineStr">
+        <is>
+          <t>70538.1074623027</t>
+        </is>
+      </c>
+    </row>
+    <row r="6270">
+      <c r="A6270" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B6270" t="inlineStr">
+        <is>
+          <t>70930.0132793688</t>
+        </is>
+      </c>
+    </row>
+    <row r="6271">
+      <c r="A6271" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B6271" t="inlineStr">
+        <is>
+          <t>71136.2179199299</t>
+        </is>
+      </c>
+    </row>
+    <row r="6272">
+      <c r="A6272" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B6272" t="inlineStr">
+        <is>
+          <t>70748.0100000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6273">
+      <c r="A6273" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B6273" t="inlineStr">
+        <is>
+          <t>72798.2300000000</t>
         </is>
       </c>
     </row>

--- a/data_cripto/btc_price.xlsx
+++ b/data_cripto/btc_price.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6273"/>
+  <dimension ref="A1:B6279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75688,7 +75688,7 @@
       </c>
       <c r="B6272" t="inlineStr">
         <is>
-          <t>70748.0100000000</t>
+          <t>72712.1461957919</t>
         </is>
       </c>
     </row>
@@ -75700,7 +75700,79 @@
       </c>
       <c r="B6273" t="inlineStr">
         <is>
-          <t>72798.2300000000</t>
+          <t>74723.9575534775</t>
+        </is>
+      </c>
+    </row>
+    <row r="6274">
+      <c r="A6274" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B6274" t="inlineStr">
+        <is>
+          <t>74086.0136095850</t>
+        </is>
+      </c>
+    </row>
+    <row r="6275">
+      <c r="A6275" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B6275" t="inlineStr">
+        <is>
+          <t>71253.9579275278</t>
+        </is>
+      </c>
+    </row>
+    <row r="6276">
+      <c r="A6276" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B6276" t="inlineStr">
+        <is>
+          <t>69948.9048267095</t>
+        </is>
+      </c>
+    </row>
+    <row r="6277">
+      <c r="A6277" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B6277" t="inlineStr">
+        <is>
+          <t>70510.4196797194</t>
+        </is>
+      </c>
+    </row>
+    <row r="6278">
+      <c r="A6278" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B6278" t="inlineStr">
+        <is>
+          <t>70755.5000000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6279">
+      <c r="A6279" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B6279" t="inlineStr">
+        <is>
+          <t>70277.2100000000</t>
         </is>
       </c>
     </row>
